--- a/config.xlsx
+++ b/config.xlsx
@@ -1,119 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3E95B8-C539-4405-87A4-416F503C7F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="3430" yWindow="2760" windowWidth="17800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="quizzen" sheetId="1" r:id="rId1"/>
+    <sheet name="favorieten" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="29">
-  <si>
-    <t>quiznaam</t>
-  </si>
-  <si>
-    <t>taal</t>
-  </si>
-  <si>
-    <t>boek</t>
-  </si>
-  <si>
-    <t>hoofdstuk</t>
-  </si>
-  <si>
-    <t>volgnrVanaf</t>
-  </si>
-  <si>
-    <t>volgnrTot</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>Latijn-PN1-C1  Theātrum</t>
-  </si>
-  <si>
-    <t>Latijn</t>
-  </si>
-  <si>
-    <t>Pegasus novus 1</t>
-  </si>
-  <si>
-    <t>Latijn-PN1-C2 Thermae</t>
-  </si>
-  <si>
-    <t>Latijn-PN1-C3 Templum</t>
-  </si>
-  <si>
-    <t>Latijn-PN1-Caput 1-3</t>
-  </si>
-  <si>
-    <t>Latijn-PN1-C4 Lūdus</t>
-  </si>
-  <si>
-    <t>Latijn-PN1-C5 Domus</t>
-  </si>
-  <si>
-    <t>Latijn-PN1-C6 Rōmānum</t>
-  </si>
-  <si>
-    <t>Latijn-PN1-Caput 4-6</t>
-  </si>
-  <si>
-    <t>Latijn-PN1-Caput 1-6</t>
-  </si>
-  <si>
-    <t>Latijn-PN1-C7 Amphitheātrum</t>
-  </si>
-  <si>
-    <t>Latijn-PN1-C8 Circus Maximus</t>
-  </si>
-  <si>
-    <t>Latijn-PN1-Caput 7-8</t>
-  </si>
-  <si>
-    <t>Latijn-PN1-Caput 1-8</t>
-  </si>
-  <si>
-    <t>Grieks-PN1-C9 Grieks</t>
-  </si>
-  <si>
-    <t>Grieks</t>
-  </si>
-  <si>
-    <t>Elin</t>
-  </si>
-  <si>
-    <t>Pegasus Novus 1</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -143,21 +66,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -482,42 +397,41 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G18"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>quiznaam</v>
+      </c>
+      <c r="B1" t="str">
+        <v>taal</v>
+      </c>
+      <c r="C1" t="str">
+        <v>boek</v>
+      </c>
+      <c r="D1" t="str">
+        <v>hoofdstuk</v>
+      </c>
+      <c r="E1" t="str">
+        <v>volgnrVanaf</v>
+      </c>
+      <c r="F1" t="str">
+        <v>volgnrTot</v>
+      </c>
+      <c r="G1" t="str">
+        <v>type</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Latijn-PN1-C1  Theātrum</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Latijn</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Pegasus novus 1</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -528,19 +442,19 @@
       <c r="F2">
         <v>131</v>
       </c>
-      <c r="G2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
+      <c r="G2" t="str">
+        <v>M</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Latijn-PN1-C2 Thermae</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Latijn</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Pegasus novus 1</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -551,19 +465,19 @@
       <c r="F3">
         <v>216</v>
       </c>
-      <c r="G3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
+      <c r="G3" t="str">
+        <v>M</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Latijn-PN1-C3 Templum</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Latijn</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Pegasus novus 1</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -574,19 +488,19 @@
       <c r="F4">
         <v>305</v>
       </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
+      <c r="G4" t="str">
+        <v>M</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Latijn-PN1-Caput 1-3</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Latijn</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Pegasus novus 1</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -594,19 +508,19 @@
       <c r="F5">
         <v>305</v>
       </c>
-      <c r="G5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
+      <c r="G5" t="str">
+        <v>M</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Latijn-PN1-C4 Lūdus</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Latijn</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Pegasus novus 1</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -617,19 +531,19 @@
       <c r="F6">
         <v>384</v>
       </c>
-      <c r="G6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
+      <c r="G6" t="str">
+        <v>M</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Latijn-PN1-C5 Domus</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Latijn</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Pegasus novus 1</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -640,19 +554,19 @@
       <c r="F7">
         <v>473</v>
       </c>
-      <c r="G7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
+      <c r="G7" t="str">
+        <v>M</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Latijn-PN1-C6 Rōmānum</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Latijn</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Pegasus novus 1</v>
       </c>
       <c r="D8">
         <v>6</v>
@@ -663,19 +577,19 @@
       <c r="F8">
         <v>557</v>
       </c>
-      <c r="G8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>9</v>
+      <c r="G8" t="str">
+        <v>M</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Latijn-PN1-Caput 4-6</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Latijn</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Pegasus novus 1</v>
       </c>
       <c r="E9">
         <v>306</v>
@@ -683,19 +597,19 @@
       <c r="F9">
         <v>557</v>
       </c>
-      <c r="G9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>9</v>
+      <c r="G9" t="str">
+        <v>M</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Latijn-PN1-Caput 1-6</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Latijn</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Pegasus novus 1</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -703,19 +617,19 @@
       <c r="F10">
         <v>557</v>
       </c>
-      <c r="G10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
-        <v>9</v>
+      <c r="G10" t="str">
+        <v>M</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Latijn-PN1-C7 Amphitheātrum</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Latijn</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Pegasus novus 1</v>
       </c>
       <c r="D11">
         <v>7</v>
@@ -726,19 +640,19 @@
       <c r="F11">
         <v>617</v>
       </c>
-      <c r="G11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
-        <v>9</v>
+      <c r="G11" t="str">
+        <v>M</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Latijn-PN1-C8 Circus Maximus</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Latijn</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Pegasus novus 1</v>
       </c>
       <c r="D12">
         <v>8</v>
@@ -749,19 +663,19 @@
       <c r="F12">
         <v>688</v>
       </c>
-      <c r="G12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
-        <v>9</v>
+      <c r="G12" t="str">
+        <v>M</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Latijn-PN1-Caput 7-8</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Latijn</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Pegasus novus 1</v>
       </c>
       <c r="E13">
         <v>558</v>
@@ -769,19 +683,19 @@
       <c r="F13">
         <v>688</v>
       </c>
-      <c r="G13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
-        <v>9</v>
+      <c r="G13" t="str">
+        <v>M</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Latijn-PN1-Caput 1-8</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Latijn</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Pegasus novus 1</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -789,19 +703,19 @@
       <c r="F14">
         <v>688</v>
       </c>
-      <c r="G14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" t="s">
-        <v>9</v>
+      <c r="G14" t="str">
+        <v>M</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Grieks-PN1-C9 Grieks</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Grieks</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Pegasus novus 1</v>
       </c>
       <c r="D15">
         <v>9</v>
@@ -812,22 +726,22 @@
       <c r="F15">
         <v>31</v>
       </c>
-      <c r="G15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="G15" t="str">
+        <v>M</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Elin</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Latijn</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Pegasus Novus 1</v>
+      </c>
+      <c r="D16" t="str">
         <v>8</v>
-      </c>
-      <c r="C16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" t="s">
-        <v>26</v>
       </c>
       <c r="E16">
         <v>618</v>
@@ -835,14 +749,155 @@
       <c r="F16">
         <v>650</v>
       </c>
-      <c r="G16" t="s">
-        <v>27</v>
+      <c r="G16" t="str">
+        <v>T</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Favo</v>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v>F</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>x</v>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v>F</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G1 A16:G16 A2:F2 A3:F3 A4:F4 A5:F15" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>favoriet</v>
+      </c>
+      <c r="B1" t="str">
+        <v>taal</v>
+      </c>
+      <c r="C1" t="str">
+        <v>boek</v>
+      </c>
+      <c r="D1" t="str">
+        <v>hoofdstuk</v>
+      </c>
+      <c r="E1" t="str">
+        <v>volgnr</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Favo</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Latijn</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Pegasus Novus 1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Favo</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Latijn</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Pegasus Novus 1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Favo</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Latijn</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Pegasus Novus 1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Favo</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Latijn</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Pegasus Novus 1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>x</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Latijn</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Pegasus Novus 1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>116</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config.xlsx
+++ b/config.xlsx
@@ -3,8 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="quizzen" sheetId="1" r:id="rId1"/>
-    <sheet name="favorieten" sheetId="2" r:id="rId2"/>
+    <sheet name="gebruikers" sheetId="1" r:id="rId1"/>
+    <sheet name="quizzen" sheetId="2" r:id="rId2"/>
+    <sheet name="favorieten" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -398,6 +399,62 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>gebruikersnaam</v>
+      </c>
+      <c r="B1" t="str">
+        <v>wachtwoord</v>
+      </c>
+      <c r="C1" t="str">
+        <v>rol</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>wim@so-be-it-services.be</v>
+      </c>
+      <c r="B2" t="str">
+        <v>$2b$10$ggqIrgQS7sg15eIlUW.m1.sT3b58627joKMT2q24ur1G5GfbKE3Va</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Admin</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Gast</v>
+      </c>
+      <c r="B3" t="str">
+        <v>$2b$10$lmLJ/k7PFylHD9Sn5QKT1.8vVMK0TrljqtdaL6KcaHPO6o8N/sLQW</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Guest</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>elin@myntuus.be</v>
+      </c>
+      <c r="B4" t="str">
+        <v>$2b$10$Zcldi3thb2Qi71j3wP6QT.WgwRsYaL303yLWb2WR.dJmp6SsDaBvO</v>
+      </c>
+      <c r="C4" t="str">
+        <v>User</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G18"/>
   <sheetData>
     <row r="1">
@@ -769,29 +826,37 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>x</v>
+        <v>ElinX</v>
       </c>
       <c r="B18" t="str">
-        <v/>
+        <v>Latijn</v>
       </c>
       <c r="C18" t="str">
-        <v/>
+        <v>Pegasus Novus 1</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <v>132</v>
+      </c>
+      <c r="F18">
+        <v>216</v>
       </c>
       <c r="G18" t="str">
-        <v>F</v>
+        <v>T</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:G18"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -878,26 +943,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>x</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Latijn</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Pegasus Novus 1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>116</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config.xlsx
+++ b/config.xlsx
@@ -1,43 +1,190 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7F2E4F-1485-4539-B8A8-8E63764796CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="gebruikers" sheetId="1" r:id="rId1"/>
     <sheet name="quizzen" sheetId="2" r:id="rId2"/>
     <sheet name="favorieten" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="52">
+  <si>
+    <t>gebruikersnaam</t>
+  </si>
+  <si>
+    <t>wachtwoord</t>
+  </si>
+  <si>
+    <t>rol</t>
+  </si>
+  <si>
+    <t>wim@so-be-it-services.be</t>
+  </si>
+  <si>
+    <t>$2b$10$ggqIrgQS7sg15eIlUW.m1.sT3b58627joKMT2q24ur1G5GfbKE3Va</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Gast</t>
+  </si>
+  <si>
+    <t>$2b$10$lmLJ/k7PFylHD9Sn5QKT1.8vVMK0TrljqtdaL6KcaHPO6o8N/sLQW</t>
+  </si>
+  <si>
+    <t>Guest</t>
+  </si>
+  <si>
+    <t>elin@myntuus.be</t>
+  </si>
+  <si>
+    <t>$2b$10$Zcldi3thb2Qi71j3wP6QT.WgwRsYaL303yLWb2WR.dJmp6SsDaBvO</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>quiznaam</t>
+  </si>
+  <si>
+    <t>taal</t>
+  </si>
+  <si>
+    <t>boek</t>
+  </si>
+  <si>
+    <t>hoofdstuk</t>
+  </si>
+  <si>
+    <t>volgnrVanaf</t>
+  </si>
+  <si>
+    <t>volgnrTot</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Latijn-PN1-C1  Theātrum</t>
+  </si>
+  <si>
+    <t>Latijn</t>
+  </si>
+  <si>
+    <t>Pegasus novus 1</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Latijn-PN1-C2 Thermae</t>
+  </si>
+  <si>
+    <t>Latijn-PN1-C3 Templum</t>
+  </si>
+  <si>
+    <t>Latijn-PN1-Caput 1-3</t>
+  </si>
+  <si>
+    <t>Latijn-PN1-C4 Lūdus</t>
+  </si>
+  <si>
+    <t>Latijn-PN1-C5 Domus</t>
+  </si>
+  <si>
+    <t>Latijn-PN1-C6 Rōmānum</t>
+  </si>
+  <si>
+    <t>Latijn-PN1-Caput 4-6</t>
+  </si>
+  <si>
+    <t>Latijn-PN1-Caput 1-6</t>
+  </si>
+  <si>
+    <t>Latijn-PN1-C7 Amphitheātrum</t>
+  </si>
+  <si>
+    <t>Latijn-PN1-C8 Circus Maximus</t>
+  </si>
+  <si>
+    <t>Latijn-PN1-Caput 7-8</t>
+  </si>
+  <si>
+    <t>Latijn-PN1-Caput 1-8</t>
+  </si>
+  <si>
+    <t>Grieks-PN1-C9 Grieks</t>
+  </si>
+  <si>
+    <t>Grieks</t>
+  </si>
+  <si>
+    <t>Elin</t>
+  </si>
+  <si>
+    <t>Pegasus Novus 1</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>Favo</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>ElinX</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>favoriet</t>
+  </si>
+  <si>
+    <t>volgnr</t>
+  </si>
+  <si>
+    <t>owen@myntuus.be</t>
+  </si>
+  <si>
+    <t>iain@myntuus.be</t>
+  </si>
+  <si>
+    <t>$2b$10$NlsadsKDix2KMW3IO5nRCu2lSM4P5i0Ox..0VSwDFERgEHTFdGC46</t>
+  </si>
+  <si>
+    <t>$2b$10$VYfiGAX3JhthLEoTEgDb8.ElyFrKlsmQGEnZPuI1oaiyAgXvMefuq</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -67,13 +214,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -398,97 +553,125 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="62.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>gebruikersnaam</v>
-      </c>
-      <c r="B1" t="str">
-        <v>wachtwoord</v>
-      </c>
-      <c r="C1" t="str">
-        <v>rol</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>wim@so-be-it-services.be</v>
-      </c>
-      <c r="B2" t="str">
-        <v>$2b$10$ggqIrgQS7sg15eIlUW.m1.sT3b58627joKMT2q24ur1G5GfbKE3Va</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Admin</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Gast</v>
-      </c>
-      <c r="B3" t="str">
-        <v>$2b$10$lmLJ/k7PFylHD9Sn5QKT1.8vVMK0TrljqtdaL6KcaHPO6o8N/sLQW</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Guest</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>elin@myntuus.be</v>
-      </c>
-      <c r="B4" t="str">
-        <v>$2b$10$Zcldi3thb2Qi71j3wP6QT.WgwRsYaL303yLWb2WR.dJmp6SsDaBvO</v>
-      </c>
-      <c r="C4" t="str">
-        <v>User</v>
+    <row r="1" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+    <ignoredError sqref="A1:C4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>quiznaam</v>
-      </c>
-      <c r="B1" t="str">
-        <v>taal</v>
-      </c>
-      <c r="C1" t="str">
-        <v>boek</v>
-      </c>
-      <c r="D1" t="str">
-        <v>hoofdstuk</v>
-      </c>
-      <c r="E1" t="str">
-        <v>volgnrVanaf</v>
-      </c>
-      <c r="F1" t="str">
-        <v>volgnrTot</v>
-      </c>
-      <c r="G1" t="str">
-        <v>type</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Latijn-PN1-C1  Theātrum</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Latijn</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Pegasus novus 1</v>
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -499,19 +682,19 @@
       <c r="F2">
         <v>131</v>
       </c>
-      <c r="G2" t="str">
-        <v>M</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Latijn-PN1-C2 Thermae</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Latijn</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Pegasus novus 1</v>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -522,19 +705,19 @@
       <c r="F3">
         <v>216</v>
       </c>
-      <c r="G3" t="str">
-        <v>M</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Latijn-PN1-C3 Templum</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Latijn</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Pegasus novus 1</v>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -545,19 +728,19 @@
       <c r="F4">
         <v>305</v>
       </c>
-      <c r="G4" t="str">
-        <v>M</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Latijn-PN1-Caput 1-3</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Latijn</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Pegasus novus 1</v>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -565,19 +748,19 @@
       <c r="F5">
         <v>305</v>
       </c>
-      <c r="G5" t="str">
-        <v>M</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Latijn-PN1-C4 Lūdus</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Latijn</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Pegasus novus 1</v>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -588,19 +771,19 @@
       <c r="F6">
         <v>384</v>
       </c>
-      <c r="G6" t="str">
-        <v>M</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Latijn-PN1-C5 Domus</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Latijn</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Pegasus novus 1</v>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -611,19 +794,19 @@
       <c r="F7">
         <v>473</v>
       </c>
-      <c r="G7" t="str">
-        <v>M</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Latijn-PN1-C6 Rōmānum</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Latijn</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Pegasus novus 1</v>
+      <c r="G7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
       </c>
       <c r="D8">
         <v>6</v>
@@ -634,19 +817,19 @@
       <c r="F8">
         <v>557</v>
       </c>
-      <c r="G8" t="str">
-        <v>M</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Latijn-PN1-Caput 4-6</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Latijn</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Pegasus novus 1</v>
+      <c r="G8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
       </c>
       <c r="E9">
         <v>306</v>
@@ -654,19 +837,19 @@
       <c r="F9">
         <v>557</v>
       </c>
-      <c r="G9" t="str">
-        <v>M</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Latijn-PN1-Caput 1-6</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Latijn</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Pegasus novus 1</v>
+      <c r="G9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -674,19 +857,19 @@
       <c r="F10">
         <v>557</v>
       </c>
-      <c r="G10" t="str">
-        <v>M</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Latijn-PN1-C7 Amphitheātrum</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Latijn</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Pegasus novus 1</v>
+      <c r="G10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
       </c>
       <c r="D11">
         <v>7</v>
@@ -697,19 +880,19 @@
       <c r="F11">
         <v>617</v>
       </c>
-      <c r="G11" t="str">
-        <v>M</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Latijn-PN1-C8 Circus Maximus</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Latijn</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Pegasus novus 1</v>
+      <c r="G11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
       </c>
       <c r="D12">
         <v>8</v>
@@ -720,19 +903,19 @@
       <c r="F12">
         <v>688</v>
       </c>
-      <c r="G12" t="str">
-        <v>M</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Latijn-PN1-Caput 7-8</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Latijn</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Pegasus novus 1</v>
+      <c r="G12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
       </c>
       <c r="E13">
         <v>558</v>
@@ -740,19 +923,19 @@
       <c r="F13">
         <v>688</v>
       </c>
-      <c r="G13" t="str">
-        <v>M</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Latijn-PN1-Caput 1-8</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Latijn</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Pegasus novus 1</v>
+      <c r="G13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>21</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -760,19 +943,19 @@
       <c r="F14">
         <v>688</v>
       </c>
-      <c r="G14" t="str">
-        <v>M</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Grieks-PN1-C9 Grieks</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Grieks</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Pegasus novus 1</v>
+      <c r="G14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" t="s">
+        <v>21</v>
       </c>
       <c r="D15">
         <v>9</v>
@@ -783,22 +966,22 @@
       <c r="F15">
         <v>31</v>
       </c>
-      <c r="G15" t="str">
-        <v>M</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Elin</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Latijn</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Pegasus Novus 1</v>
-      </c>
-      <c r="D16" t="str">
-        <v>8</v>
+      <c r="G15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" t="s">
+        <v>39</v>
       </c>
       <c r="E16">
         <v>618</v>
@@ -806,36 +989,36 @@
       <c r="F16">
         <v>650</v>
       </c>
-      <c r="G16" t="str">
-        <v>T</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Favo</v>
-      </c>
-      <c r="B17" t="str">
-        <v/>
-      </c>
-      <c r="C17" t="str">
-        <v/>
-      </c>
-      <c r="G17" t="str">
-        <v>F</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>ElinX</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Latijn</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Pegasus Novus 1</v>
-      </c>
-      <c r="D18" t="str">
-        <v>2</v>
+      <c r="G16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" t="s">
+        <v>45</v>
       </c>
       <c r="E18">
         <v>132</v>
@@ -843,47 +1026,49 @@
       <c r="F18">
         <v>216</v>
       </c>
-      <c r="G18" t="str">
-        <v>T</v>
+      <c r="G18" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G18"/>
+    <ignoredError sqref="A1:G18" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>favoriet</v>
-      </c>
-      <c r="B1" t="str">
-        <v>taal</v>
-      </c>
-      <c r="C1" t="str">
-        <v>boek</v>
-      </c>
-      <c r="D1" t="str">
-        <v>hoofdstuk</v>
-      </c>
-      <c r="E1" t="str">
-        <v>volgnr</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Favo</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Latijn</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Pegasus Novus 1</v>
+    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>38</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -892,15 +1077,15 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Favo</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Latijn</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Pegasus Novus 1</v>
+    <row r="3" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -909,15 +1094,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Favo</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Latijn</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Pegasus Novus 1</v>
+    <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -926,15 +1111,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Favo</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Latijn</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Pegasus Novus 1</v>
+    <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -944,8 +1129,9 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError sqref="A1:E5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config.xlsx
+++ b/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7F2E4F-1485-4539-B8A8-8E63764796CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A571C84A-A96A-4BEE-8002-022A37482545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="gebruikers" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="48">
   <si>
     <t>gebruikersnaam</t>
   </si>
@@ -135,33 +135,12 @@
     <t>Grieks</t>
   </si>
   <si>
-    <t>Elin</t>
-  </si>
-  <si>
     <t>Pegasus Novus 1</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
     <t>Favo</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>ElinX</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>favoriet</t>
   </si>
   <si>
@@ -178,6 +157,15 @@
   </si>
   <si>
     <t>$2b$10$VYfiGAX3JhthLEoTEgDb8.ElyFrKlsmQGEnZPuI1oaiyAgXvMefuq</t>
+  </si>
+  <si>
+    <t>Frans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Van In Zouff 5 </t>
+  </si>
+  <si>
+    <t>Frans-VIZ5-10-Voilà mon école</t>
   </si>
 </sst>
 </file>
@@ -555,13 +543,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.08203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="62.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -572,7 +560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -583,7 +571,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -594,7 +582,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -605,23 +593,23 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
@@ -637,10 +625,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.08203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -663,7 +655,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -686,7 +678,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -709,7 +701,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -732,7 +724,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -752,7 +744,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -775,7 +767,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -798,7 +790,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -821,7 +813,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -841,7 +833,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -861,7 +853,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -884,7 +876,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -907,7 +899,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -927,7 +919,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -947,7 +939,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -970,70 +962,33 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" t="s">
-        <v>39</v>
+        <v>46</v>
+      </c>
+      <c r="D16">
+        <v>10</v>
       </c>
       <c r="E16">
-        <v>618</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>650</v>
+        <v>31</v>
       </c>
       <c r="G16" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18">
-        <v>132</v>
-      </c>
-      <c r="F18">
-        <v>216</v>
-      </c>
-      <c r="G18" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G18" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G15" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1041,11 +996,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s">
         <v>13</v>
@@ -1057,18 +1012,18 @@
         <v>15</v>
       </c>
       <c r="E1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1077,15 +1032,15 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1094,32 +1049,32 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>38</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>41</v>
-      </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5">
         <v>1</v>
